--- a/output/pdf_financials_xlsx/KDOZ.xlsx
+++ b/output/pdf_financials_xlsx/KDOZ.xlsx
@@ -2791,34 +2791,34 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.5572510000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.396384</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.787524</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.876004</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.491203</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2876386</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>570086</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>60190</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>478397</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>641536</v>
       </c>
       <c r="P34" s="1" t="inlineStr">
         <is>
@@ -2826,19 +2826,19 @@
         </is>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.078607</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.36353</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>1.469224</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>2.780517</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>0</v>
+        <v>4.454295</v>
       </c>
     </row>
     <row r="35">
@@ -2945,34 +2945,34 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.5572510000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.396384</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.787524</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.876004</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.491203</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2876386</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>570086</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>60190</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>478397</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>641536</v>
       </c>
       <c r="P36" s="1" t="inlineStr">
         <is>
@@ -2980,19 +2980,19 @@
         </is>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.078607</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2.36353</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>1.469224</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0</v>
+        <v>2.780517</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0</v>
+        <v>4.454295</v>
       </c>
     </row>
     <row r="37">
@@ -3869,25 +3869,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.673544</v>
+        <v>0.116293</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.860831</v>
+        <v>0.464447</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.154922</v>
+        <v>0.367398</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.746321</v>
+        <v>0.870317</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.884555</v>
+        <v>0.393352</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.012809</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.632239</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -3904,19 +3904,19 @@
         </is>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>8.811939000000001</v>
+        <v>6.733332</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>9.83506</v>
+        <v>7.47153</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>7.833424</v>
+        <v>6.3642</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>8.027132</v>
+        <v>5.246615</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>9.616489</v>
+        <v>5.162194</v>
       </c>
     </row>
     <row r="49">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
